--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Богдановский- председатель/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Богдановский- председатель/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.92576096404</v>
+        <v>46157.93121268053</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Богдановский- председатель/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Богдановский- председатель/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93121268053</v>
+        <v>46157.93186942676</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Богдановский- председатель/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Богдановский- председатель/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93186942676</v>
+        <v>46157.93407436289</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Богдановский- председатель/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Богдановский- председатель/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93407436289</v>
+        <v>46157.93725552726</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Богдановский- председатель/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Богдановский- председатель/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93725552726</v>
+        <v>46158.28223025497</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Богдановский- председатель/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Богдановский- председатель/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.28223025497</v>
+        <v>46158.29712792933</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Богдановский- председатель/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Богдановский- председатель/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29712792933</v>
+        <v>46158.29823205891</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Богдановский- председатель/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Богдановский- председатель/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29823205891</v>
+        <v>46158.33394067209</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Богдановский- председатель/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Богдановский- председатель/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.33394067209</v>
+        <v>46158.36863836018</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Богдановский- председатель/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Богдановский- председатель/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.36863836018</v>
+        <v>46158.37294813581</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
